--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0002T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0002T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>58.42302628245134</v>
+        <v>9.493741770898342</v>
       </c>
       <c r="D2" t="n">
-        <v>63.3581091889586</v>
+        <v>10.29569274320577</v>
       </c>
       <c r="E2" t="n">
-        <v>13.53286997194427</v>
+        <v>2.199091370440943</v>
       </c>
       <c r="F2" t="n">
-        <v>13.48186889896495</v>
+        <v>2.190803696081806</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.06453625896733</v>
+        <v>8.460487142082192</v>
       </c>
       <c r="D3" t="n">
-        <v>51.41222572685646</v>
+        <v>8.354486680614174</v>
       </c>
       <c r="E3" t="n">
-        <v>13.53286997194427</v>
+        <v>2.199091370440943</v>
       </c>
       <c r="F3" t="n">
-        <v>13.48186889896495</v>
+        <v>2.190803696081806</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>27.06931114233036</v>
+        <v>4.398763060628684</v>
       </c>
       <c r="D4" t="n">
-        <v>30.72254471046651</v>
+        <v>4.992413515450807</v>
       </c>
       <c r="E4" t="n">
-        <v>13.53286997194427</v>
+        <v>2.199091370440943</v>
       </c>
       <c r="F4" t="n">
-        <v>13.48186889896495</v>
+        <v>2.190803696081806</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
